--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/195.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/195.xlsx
@@ -426,13 +426,13 @@
         <v>-13.74114289504197</v>
       </c>
       <c r="E2">
-        <v>-10.25456844201285</v>
+        <v>-12.98042902924193</v>
       </c>
       <c r="F2">
-        <v>1.181295891385405</v>
+        <v>0.1460661352575663</v>
       </c>
       <c r="G2">
-        <v>-4.611971799610114</v>
+        <v>-6.163584767320048</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.69248632672806</v>
       </c>
       <c r="E3">
-        <v>-9.115525903337533</v>
+        <v>-15.86185628405651</v>
       </c>
       <c r="F3">
-        <v>0.9647161889194832</v>
+        <v>-0.1927907090864774</v>
       </c>
       <c r="G3">
-        <v>-5.31019564875226</v>
+        <v>-5.262719115173573</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.58631867999682</v>
       </c>
       <c r="E4">
-        <v>-10.64547084682896</v>
+        <v>-14.57520360662717</v>
       </c>
       <c r="F4">
-        <v>1.182493173057477</v>
+        <v>0.1396521263000365</v>
       </c>
       <c r="G4">
-        <v>-4.858388946280225</v>
+        <v>-5.731174551162602</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.41762752027914</v>
       </c>
       <c r="E5">
-        <v>-11.77303823236884</v>
+        <v>-16.5082642493334</v>
       </c>
       <c r="F5">
-        <v>1.188797906306841</v>
+        <v>0.4936278191658229</v>
       </c>
       <c r="G5">
-        <v>-5.20172562415804</v>
+        <v>-5.025889308385191</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.17600530215583</v>
       </c>
       <c r="E6">
-        <v>-12.95457597113214</v>
+        <v>-15.12306292054914</v>
       </c>
       <c r="F6">
-        <v>1.751097442701364</v>
+        <v>-0.2280867628238763</v>
       </c>
       <c r="G6">
-        <v>-5.579627708011385</v>
+        <v>-5.11096701819892</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.85116757282699</v>
       </c>
       <c r="E7">
-        <v>-11.22602574308631</v>
+        <v>-17.30223254015023</v>
       </c>
       <c r="F7">
-        <v>1.461470888591713</v>
+        <v>-0.2107697304915037</v>
       </c>
       <c r="G7">
-        <v>-4.962167927845298</v>
+        <v>-3.816580128344818</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.43116380599446</v>
       </c>
       <c r="E8">
-        <v>-12.57821449635466</v>
+        <v>-15.39147463193177</v>
       </c>
       <c r="F8">
-        <v>1.394920398613116</v>
+        <v>0.008683606357982838</v>
       </c>
       <c r="G8">
-        <v>-6.611329430415397</v>
+        <v>-6.940907481032001</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.920683076514</v>
       </c>
       <c r="E9">
-        <v>-15.03138849273786</v>
+        <v>-16.4967528684059</v>
       </c>
       <c r="F9">
-        <v>1.484616750545861</v>
+        <v>0.7448233736784622</v>
       </c>
       <c r="G9">
-        <v>-4.846249175787718</v>
+        <v>-6.027289607468253</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.31974847544145</v>
       </c>
       <c r="E10">
-        <v>-14.23983840704113</v>
+        <v>-18.58395823785922</v>
       </c>
       <c r="F10">
-        <v>1.732512653783682</v>
+        <v>-0.01336316369084971</v>
       </c>
       <c r="G10">
-        <v>-5.153385038193602</v>
+        <v>-4.98237218727147</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.63050741503839</v>
       </c>
       <c r="E11">
-        <v>-14.36579338309047</v>
+        <v>-19.13386442203266</v>
       </c>
       <c r="F11">
-        <v>1.936319768041584</v>
+        <v>0.4129150390384091</v>
       </c>
       <c r="G11">
-        <v>-3.485151482771762</v>
+        <v>-5.249003525004372</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.859305681277727</v>
       </c>
       <c r="E12">
-        <v>-15.63164225092857</v>
+        <v>-20.83321957815103</v>
       </c>
       <c r="F12">
-        <v>1.455704615353598</v>
+        <v>0.7646814621521575</v>
       </c>
       <c r="G12">
-        <v>-3.078762154552988</v>
+        <v>-5.398809021201933</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.017530806249137</v>
       </c>
       <c r="E13">
-        <v>-15.75265666183555</v>
+        <v>-22.47666619417071</v>
       </c>
       <c r="F13">
-        <v>1.693129055078534</v>
+        <v>0.5842324264410714</v>
       </c>
       <c r="G13">
-        <v>-2.922885117836404</v>
+        <v>-5.255492194261343</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.139133810592678</v>
       </c>
       <c r="E14">
-        <v>-17.17624133630882</v>
+        <v>-20.46135034958916</v>
       </c>
       <c r="F14">
-        <v>1.492565370535451</v>
+        <v>0.7571287686414268</v>
       </c>
       <c r="G14">
-        <v>-2.170388185123445</v>
+        <v>-4.313115611597946</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.254112189097686</v>
       </c>
       <c r="E15">
-        <v>-17.99427846647642</v>
+        <v>-22.54101580981971</v>
       </c>
       <c r="F15">
-        <v>2.02380685022229</v>
+        <v>0.8170957931295414</v>
       </c>
       <c r="G15">
-        <v>-1.495248770026637</v>
+        <v>-2.206406920590716</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.394236189435204</v>
       </c>
       <c r="E16">
-        <v>-20.09774558609129</v>
+        <v>-22.6900841172042</v>
       </c>
       <c r="F16">
-        <v>1.908544733696607</v>
+        <v>0.7698997731435304</v>
       </c>
       <c r="G16">
-        <v>-1.364055160850859</v>
+        <v>-2.252658552319874</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.586941090269652</v>
       </c>
       <c r="E17">
-        <v>-20.58014127975837</v>
+        <v>-24.94638270610394</v>
       </c>
       <c r="F17">
-        <v>2.301984794269229</v>
+        <v>0.5285010234237995</v>
       </c>
       <c r="G17">
-        <v>0.5190592844339955</v>
+        <v>-2.62115537629615</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.859004375891839</v>
       </c>
       <c r="E18">
-        <v>-19.95950033158513</v>
+        <v>-24.47774451647215</v>
       </c>
       <c r="F18">
-        <v>2.664034219891926</v>
+        <v>1.417176217842787</v>
       </c>
       <c r="G18">
-        <v>0.6830968159048828</v>
+        <v>-1.788169149886891</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.239710423402076</v>
       </c>
       <c r="E19">
-        <v>-21.37358879606431</v>
+        <v>-24.76553356813361</v>
       </c>
       <c r="F19">
-        <v>2.506152993475852</v>
+        <v>0.7921492575495392</v>
       </c>
       <c r="G19">
-        <v>1.218451756151505</v>
+        <v>-1.897907113422652</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.7443355756395</v>
       </c>
       <c r="E20">
-        <v>-22.79532585314246</v>
+        <v>-25.70055929581537</v>
       </c>
       <c r="F20">
-        <v>2.858795205960838</v>
+        <v>1.824003344518619</v>
       </c>
       <c r="G20">
-        <v>1.923346354555283</v>
+        <v>0.6158530149112065</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.381173970851079</v>
       </c>
       <c r="E21">
-        <v>-22.92414735323866</v>
+        <v>-26.31330711379324</v>
       </c>
       <c r="F21">
-        <v>2.722409619935024</v>
+        <v>1.375470906265605</v>
       </c>
       <c r="G21">
-        <v>3.18918309967871</v>
+        <v>0.8249669344448103</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.147946557373508</v>
       </c>
       <c r="E22">
-        <v>-24.3383807288861</v>
+        <v>-27.28170769491152</v>
       </c>
       <c r="F22">
-        <v>2.418840118945844</v>
+        <v>1.568923751248364</v>
       </c>
       <c r="G22">
-        <v>2.846862759281452</v>
+        <v>-0.5700141921655861</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.04542641941971</v>
       </c>
       <c r="E23">
-        <v>-23.88457329162944</v>
+        <v>-27.64960092329466</v>
       </c>
       <c r="F23">
-        <v>3.106185907011634</v>
+        <v>1.918351040725008</v>
       </c>
       <c r="G23">
-        <v>2.654390952173765</v>
+        <v>0.4716588934027107</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.071122222321557</v>
       </c>
       <c r="E24">
-        <v>-24.83118738429682</v>
+        <v>-29.87129970653879</v>
       </c>
       <c r="F24">
-        <v>3.081731903971334</v>
+        <v>1.508586139576036</v>
       </c>
       <c r="G24">
-        <v>2.904601984031881</v>
+        <v>1.651547255235579</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.214722177925245</v>
       </c>
       <c r="E25">
-        <v>-25.5406407647085</v>
+        <v>-29.74101777357512</v>
       </c>
       <c r="F25">
-        <v>2.601384397583057</v>
+        <v>1.814019662427688</v>
       </c>
       <c r="G25">
-        <v>2.404554011961586</v>
+        <v>-0.2152230267218931</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.461072354082572</v>
       </c>
       <c r="E26">
-        <v>-25.84768941632457</v>
+        <v>-29.24747750537516</v>
       </c>
       <c r="F26">
-        <v>2.766085061671013</v>
+        <v>1.669001295456814</v>
       </c>
       <c r="G26">
-        <v>2.747937037476951</v>
+        <v>0.2097682568820456</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.789533896454892</v>
       </c>
       <c r="E27">
-        <v>-26.70512879883291</v>
+        <v>-26.63793077303309</v>
       </c>
       <c r="F27">
-        <v>3.103194286537369</v>
+        <v>2.60365068074805</v>
       </c>
       <c r="G27">
-        <v>3.383866351206632</v>
+        <v>0.8217126681797067</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.186122591114276</v>
       </c>
       <c r="E28">
-        <v>-26.29233575066372</v>
+        <v>-29.06662836740484</v>
       </c>
       <c r="F28">
-        <v>2.914706359599512</v>
+        <v>2.074122770861717</v>
       </c>
       <c r="G28">
-        <v>3.163072827010479</v>
+        <v>1.759232680536993</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.63278360480433</v>
       </c>
       <c r="E29">
-        <v>-26.06073600448943</v>
+        <v>-28.41833655694075</v>
       </c>
       <c r="F29">
-        <v>3.340751757559202</v>
+        <v>0.9543666707620864</v>
       </c>
       <c r="G29">
-        <v>2.926123840582683</v>
+        <v>0.8563343534294048</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.109676636059903</v>
       </c>
       <c r="E30">
-        <v>-25.28344608344286</v>
+        <v>-29.0027315991566</v>
       </c>
       <c r="F30">
-        <v>2.731148509176418</v>
+        <v>2.088482232397006</v>
       </c>
       <c r="G30">
-        <v>2.344371604603175</v>
+        <v>1.512226256760891</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.595343369450104</v>
       </c>
       <c r="E31">
-        <v>-25.70348921849833</v>
+        <v>-28.64781244880544</v>
       </c>
       <c r="F31">
-        <v>3.241437559601994</v>
+        <v>1.690927703856073</v>
       </c>
       <c r="G31">
-        <v>2.577655817118998</v>
+        <v>0.3769541171607798</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.070278921669479</v>
       </c>
       <c r="E32">
-        <v>-25.21838549737466</v>
+        <v>-25.27073918537733</v>
       </c>
       <c r="F32">
-        <v>2.681754305379778</v>
+        <v>2.296343633798434</v>
       </c>
       <c r="G32">
-        <v>1.563566196983909</v>
+        <v>0.8471475895579272</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.523594409932396</v>
       </c>
       <c r="E33">
-        <v>-25.47567980506846</v>
+        <v>-27.6254188720937</v>
       </c>
       <c r="F33">
-        <v>3.098821674504841</v>
+        <v>2.359519246471229</v>
       </c>
       <c r="G33">
-        <v>2.250848693118764</v>
+        <v>-0.8915145116663682</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.943878832531543</v>
       </c>
       <c r="E34">
-        <v>-25.17890173250178</v>
+        <v>-25.98540031089783</v>
       </c>
       <c r="F34">
-        <v>3.629295056822692</v>
+        <v>2.220058103557631</v>
       </c>
       <c r="G34">
-        <v>1.918632137707361</v>
+        <v>-0.5254939757534672</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.321574360640256</v>
       </c>
       <c r="E35">
-        <v>-24.37701314064553</v>
+        <v>-28.4234990173095</v>
       </c>
       <c r="F35">
-        <v>3.581066460579814</v>
+        <v>1.83276757305466</v>
       </c>
       <c r="G35">
-        <v>1.102857437556773</v>
+        <v>-1.458266665807438</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.646005915315325</v>
       </c>
       <c r="E36">
-        <v>-23.45801821095094</v>
+        <v>-27.31832946421155</v>
       </c>
       <c r="F36">
-        <v>3.49796466007896</v>
+        <v>2.026457973924736</v>
       </c>
       <c r="G36">
-        <v>1.130142953891446</v>
+        <v>-1.382792848603134</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.912858975651614</v>
       </c>
       <c r="E37">
-        <v>-21.99269912002297</v>
+        <v>-24.48872606594076</v>
       </c>
       <c r="F37">
-        <v>3.904342014274807</v>
+        <v>2.356210884813876</v>
       </c>
       <c r="G37">
-        <v>1.756100904456842</v>
+        <v>-0.9414838860361275</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.126062879425131</v>
       </c>
       <c r="E38">
-        <v>-22.38477892808108</v>
+        <v>-27.3542538485144</v>
       </c>
       <c r="F38">
-        <v>4.04627373841649</v>
+        <v>2.404222513346338</v>
       </c>
       <c r="G38">
-        <v>1.058208109868622</v>
+        <v>-0.6169312435481374</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.28935409661603</v>
       </c>
       <c r="E39">
-        <v>-21.58358319274801</v>
+        <v>-23.30029146126378</v>
       </c>
       <c r="F39">
-        <v>3.891292277531586</v>
+        <v>2.953752628944672</v>
       </c>
       <c r="G39">
-        <v>0.3634537124516319</v>
+        <v>-0.9154861719162309</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.408412973418669</v>
       </c>
       <c r="E40">
-        <v>-20.57983334352585</v>
+        <v>-24.72879858698339</v>
       </c>
       <c r="F40">
-        <v>4.03814457595254</v>
+        <v>2.898910476798919</v>
       </c>
       <c r="G40">
-        <v>-0.3066304996067098</v>
+        <v>-2.437410167229981</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.484717447483936</v>
       </c>
       <c r="E41">
-        <v>-20.70781707593063</v>
+        <v>-21.70562556725472</v>
       </c>
       <c r="F41">
-        <v>4.024442352372158</v>
+        <v>3.155695721340102</v>
       </c>
       <c r="G41">
-        <v>0.2048785811205421</v>
+        <v>-3.479669219358729</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.527353178146038</v>
       </c>
       <c r="E42">
-        <v>-20.69438562202388</v>
+        <v>-22.51886251497419</v>
       </c>
       <c r="F42">
-        <v>4.259988516881382</v>
+        <v>3.234390068278288</v>
       </c>
       <c r="G42">
-        <v>0.7842604664939318</v>
+        <v>-1.348230753173143</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.548339370043264</v>
       </c>
       <c r="E43">
-        <v>-18.56087660584213</v>
+        <v>-22.38098859533666</v>
       </c>
       <c r="F43">
-        <v>4.54324382209322</v>
+        <v>3.213504154665473</v>
       </c>
       <c r="G43">
-        <v>-0.5641942531075474</v>
+        <v>-2.807108719237012</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.555291283840738</v>
       </c>
       <c r="E44">
-        <v>-17.7422326601575</v>
+        <v>-22.33657785074343</v>
       </c>
       <c r="F44">
-        <v>4.555058268222398</v>
+        <v>3.471119261106346</v>
       </c>
       <c r="G44">
-        <v>-0.3777840548822654</v>
+        <v>-3.351531243715698</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.553181903231403</v>
       </c>
       <c r="E45">
-        <v>-17.1664281331342</v>
+        <v>-19.58835565886448</v>
       </c>
       <c r="F45">
-        <v>4.790493573317542</v>
+        <v>3.182653563432713</v>
       </c>
       <c r="G45">
-        <v>-0.09184230501879519</v>
+        <v>-3.296566256127179</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.539529464246463</v>
       </c>
       <c r="E46">
-        <v>-16.04806713525192</v>
+        <v>-19.64163768403873</v>
       </c>
       <c r="F46">
-        <v>4.970557768491176</v>
+        <v>3.944865881239072</v>
       </c>
       <c r="G46">
-        <v>-1.777985911808093</v>
+        <v>-3.717677580359092</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.519774972403066</v>
       </c>
       <c r="E47">
-        <v>-15.88354767455325</v>
+        <v>-20.24202729644967</v>
       </c>
       <c r="F47">
-        <v>4.865687930182607</v>
+        <v>3.025922107511247</v>
       </c>
       <c r="G47">
-        <v>-1.218626205856215</v>
+        <v>-3.573695333765109</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.498536204249389</v>
       </c>
       <c r="E48">
-        <v>-14.08934815881822</v>
+        <v>-17.22986299703365</v>
       </c>
       <c r="F48">
-        <v>5.061666786100492</v>
+        <v>3.284622052504197</v>
       </c>
       <c r="G48">
-        <v>-1.580972036220525</v>
+        <v>-4.872938793925322</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.476312247632203</v>
       </c>
       <c r="E49">
-        <v>-13.44697506388217</v>
+        <v>-17.64667280164764</v>
       </c>
       <c r="F49">
-        <v>4.66588284077302</v>
+        <v>3.591015301140605</v>
       </c>
       <c r="G49">
-        <v>-0.9278378173232517</v>
+        <v>-4.004453587698458</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.451478301067501</v>
       </c>
       <c r="E50">
-        <v>-13.66325498248851</v>
+        <v>-15.60681262794452</v>
       </c>
       <c r="F50">
-        <v>5.028051044339374</v>
+        <v>3.595294474524122</v>
       </c>
       <c r="G50">
-        <v>-1.588043361492408</v>
+        <v>-2.708586883988302</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.418738573843875</v>
       </c>
       <c r="E51">
-        <v>-12.89723643324702</v>
+        <v>-16.88848851243943</v>
       </c>
       <c r="F51">
-        <v>4.658783087154105</v>
+        <v>3.581704694063736</v>
       </c>
       <c r="G51">
-        <v>-1.472217304709927</v>
+        <v>-4.331429549521195</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.383825764117873</v>
       </c>
       <c r="E52">
-        <v>-12.17515313882795</v>
+        <v>-15.50232261869153</v>
       </c>
       <c r="F52">
-        <v>5.330752674486893</v>
+        <v>4.518846832465875</v>
       </c>
       <c r="G52">
-        <v>-1.712162334850764</v>
+        <v>-2.751177052351025</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.350913378898433</v>
       </c>
       <c r="E53">
-        <v>-11.9465286000767</v>
+        <v>-14.67733428092216</v>
       </c>
       <c r="F53">
-        <v>5.180249933930852</v>
+        <v>4.416221105439483</v>
       </c>
       <c r="G53">
-        <v>-1.613772921423624</v>
+        <v>-2.095281838474</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.32107020851031</v>
       </c>
       <c r="E54">
-        <v>-10.7138009911307</v>
+        <v>-13.44440289064581</v>
       </c>
       <c r="F54">
-        <v>5.249429375729077</v>
+        <v>4.494706403196831</v>
       </c>
       <c r="G54">
-        <v>-1.781074650796233</v>
+        <v>-4.019774792454205</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.292481306241676</v>
       </c>
       <c r="E55">
-        <v>-9.678822785151649</v>
+        <v>-16.10793809010733</v>
       </c>
       <c r="F55">
-        <v>5.233240733861455</v>
+        <v>4.105713388834763</v>
       </c>
       <c r="G55">
-        <v>-2.538388427268831</v>
+        <v>-3.07057848597991</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.260758080170246</v>
       </c>
       <c r="E56">
-        <v>-8.005986372822187</v>
+        <v>-13.10258914407285</v>
       </c>
       <c r="F56">
-        <v>5.232965169032169</v>
+        <v>4.224483413963145</v>
       </c>
       <c r="G56">
-        <v>-1.433997056459041</v>
+        <v>-2.817464105683853</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.231354661786549</v>
       </c>
       <c r="E57">
-        <v>-8.287467260190962</v>
+        <v>-13.52606033395212</v>
       </c>
       <c r="F57">
-        <v>4.954720709336781</v>
+        <v>3.870222654032579</v>
       </c>
       <c r="G57">
-        <v>-1.95324288211157</v>
+        <v>-3.374675267580743</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.204857247734182</v>
       </c>
       <c r="E58">
-        <v>-7.020440989110865</v>
+        <v>-12.45630797606817</v>
       </c>
       <c r="F58">
-        <v>4.954975685989167</v>
+        <v>4.180700280224906</v>
       </c>
       <c r="G58">
-        <v>-2.231851773605555</v>
+        <v>-3.637112144115388</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.178962959555633</v>
       </c>
       <c r="E59">
-        <v>-7.699897757695733</v>
+        <v>-12.22537391557301</v>
       </c>
       <c r="F59">
-        <v>4.866109195956113</v>
+        <v>4.039390952507991</v>
       </c>
       <c r="G59">
-        <v>-3.118922382489887</v>
+        <v>-3.960032687652517</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.147188363276143</v>
       </c>
       <c r="E60">
-        <v>-8.114669749006277</v>
+        <v>-13.66811403509874</v>
       </c>
       <c r="F60">
-        <v>4.514988924855865</v>
+        <v>3.625338959445924</v>
       </c>
       <c r="G60">
-        <v>-1.511827982087307</v>
+        <v>-3.584289079490777</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.102973907527183</v>
       </c>
       <c r="E61">
-        <v>-7.611972906362806</v>
+        <v>-11.17427434212665</v>
       </c>
       <c r="F61">
-        <v>4.975780830600296</v>
+        <v>3.908263270121435</v>
       </c>
       <c r="G61">
-        <v>-2.678474161763091</v>
+        <v>-4.947952445299668</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.049496904451356</v>
       </c>
       <c r="E62">
-        <v>-7.878677383044551</v>
+        <v>-10.75267794048655</v>
       </c>
       <c r="F62">
-        <v>4.8943672606053</v>
+        <v>4.041408593844261</v>
       </c>
       <c r="G62">
-        <v>-2.917237327146407</v>
+        <v>-4.491199787791961</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.984460301153481</v>
       </c>
       <c r="E63">
-        <v>-6.539738944722649</v>
+        <v>-9.397024904602338</v>
       </c>
       <c r="F63">
-        <v>4.646572714546067</v>
+        <v>3.598244918644586</v>
       </c>
       <c r="G63">
-        <v>-2.329473140467583</v>
+        <v>-5.332167739496403</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.90509300745589</v>
       </c>
       <c r="E64">
-        <v>-5.318210251997616</v>
+        <v>-8.624775175126297</v>
       </c>
       <c r="F64">
-        <v>4.14617390756241</v>
+        <v>3.033308511900857</v>
       </c>
       <c r="G64">
-        <v>-2.732247352957473</v>
+        <v>-4.007962765970086</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.805209894631286</v>
       </c>
       <c r="E65">
-        <v>-5.294213868230971</v>
+        <v>-10.00139504566602</v>
       </c>
       <c r="F65">
-        <v>4.080958481670529</v>
+        <v>3.386853436757644</v>
       </c>
       <c r="G65">
-        <v>-1.856495499271909</v>
+        <v>-3.950991587784768</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.683273436966615</v>
       </c>
       <c r="E66">
-        <v>-5.365143356613111</v>
+        <v>-11.43944819459381</v>
       </c>
       <c r="F66">
-        <v>3.896030725630581</v>
+        <v>2.782799493902561</v>
       </c>
       <c r="G66">
-        <v>-1.875832395766792</v>
+        <v>-4.210266893329409</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.545766049266993</v>
       </c>
       <c r="E67">
-        <v>-4.871458177244905</v>
+        <v>-8.604668750532239</v>
       </c>
       <c r="F67">
-        <v>3.951031248367877</v>
+        <v>2.70967345696306</v>
       </c>
       <c r="G67">
-        <v>-2.135696978417423</v>
+        <v>-4.759155343740571</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.394717245938389</v>
       </c>
       <c r="E68">
-        <v>-3.920619018328367</v>
+        <v>-8.797101725014183</v>
       </c>
       <c r="F68">
-        <v>3.609098055283092</v>
+        <v>1.729945466494754</v>
       </c>
       <c r="G68">
-        <v>-2.568765993137183</v>
+        <v>-4.256220575960032</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.232564535829889</v>
       </c>
       <c r="E69">
-        <v>-5.589176022720579</v>
+        <v>-8.115761111242126</v>
       </c>
       <c r="F69">
-        <v>3.85315822279372</v>
+        <v>1.849518430522264</v>
       </c>
       <c r="G69">
-        <v>-2.226624422199045</v>
+        <v>-4.630868393548274</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.057780030866081</v>
       </c>
       <c r="E70">
-        <v>-4.871317794550666</v>
+        <v>-7.128988511074724</v>
       </c>
       <c r="F70">
-        <v>3.326865824092629</v>
+        <v>2.125357240932098</v>
       </c>
       <c r="G70">
-        <v>-2.493917869039801</v>
+        <v>-3.863973898285025</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.8764966010332</v>
       </c>
       <c r="E71">
-        <v>-4.840506057402478</v>
+        <v>-9.029489425665803</v>
       </c>
       <c r="F71">
-        <v>2.975303699041972</v>
+        <v>2.389413279331064</v>
       </c>
       <c r="G71">
-        <v>-3.059554369334136</v>
+        <v>-5.248778407907701</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.696976691413302</v>
       </c>
       <c r="E72">
-        <v>-5.06324810841776</v>
+        <v>-8.575749915519257</v>
       </c>
       <c r="F72">
-        <v>2.855759241720941</v>
+        <v>2.142912621004744</v>
       </c>
       <c r="G72">
-        <v>-1.928864024760377</v>
+        <v>-6.27100203843278</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.523150852232035</v>
       </c>
       <c r="E73">
-        <v>-3.861717156910599</v>
+        <v>-8.010225024493367</v>
       </c>
       <c r="F73">
-        <v>2.510140764970928</v>
+        <v>1.913666438627138</v>
       </c>
       <c r="G73">
-        <v>-1.688362822968943</v>
+        <v>-3.916787031273018</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.357144079230469</v>
       </c>
       <c r="E74">
-        <v>-5.972357379353615</v>
+        <v>-8.881933628599873</v>
       </c>
       <c r="F74">
-        <v>2.804209614173387</v>
+        <v>1.639625134431327</v>
       </c>
       <c r="G74">
-        <v>-1.788404198620179</v>
+        <v>-3.540947417290639</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.19746806253112</v>
       </c>
       <c r="E75">
-        <v>-4.804255622971077</v>
+        <v>-9.89997081331623</v>
       </c>
       <c r="F75">
-        <v>2.863324604878995</v>
+        <v>1.162462460638999</v>
       </c>
       <c r="G75">
-        <v>-1.442597853770068</v>
+        <v>-3.346581978134488</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.051542891223767</v>
       </c>
       <c r="E76">
-        <v>-4.778724086515831</v>
+        <v>-7.734024337817537</v>
       </c>
       <c r="F76">
-        <v>2.140787287666225</v>
+        <v>1.180082772654178</v>
       </c>
       <c r="G76">
-        <v>-0.6876511173580485</v>
+        <v>-4.743340867699473</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.926565652737523</v>
       </c>
       <c r="E77">
-        <v>-6.535201413766964</v>
+        <v>-9.621066627657822</v>
       </c>
       <c r="F77">
-        <v>2.296635035686875</v>
+        <v>1.622611381781761</v>
       </c>
       <c r="G77">
-        <v>-0.6206953338262887</v>
+        <v>-2.540735604056174</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.827175001207666</v>
       </c>
       <c r="E78">
-        <v>-6.454952325877037</v>
+        <v>-11.15297240039457</v>
       </c>
       <c r="F78">
-        <v>2.114843017359496</v>
+        <v>0.6421928955343242</v>
       </c>
       <c r="G78">
-        <v>-0.08933953259110616</v>
+        <v>-2.765760005451515</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.755956197972006</v>
       </c>
       <c r="E79">
-        <v>-6.096274542099506</v>
+        <v>-10.72013632626743</v>
       </c>
       <c r="F79">
-        <v>1.936921576289451</v>
+        <v>1.896388207089694</v>
       </c>
       <c r="G79">
-        <v>-0.2834301964674973</v>
+        <v>-2.640330056059609</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.713282382143897</v>
       </c>
       <c r="E80">
-        <v>-7.043450165543838</v>
+        <v>-11.43351589364376</v>
       </c>
       <c r="F80">
-        <v>2.434545730509257</v>
+        <v>0.4073047608329649</v>
       </c>
       <c r="G80">
-        <v>0.5837605864535116</v>
+        <v>-2.788874234406707</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.708915930755963</v>
       </c>
       <c r="E81">
-        <v>-8.186889852480604</v>
+        <v>-11.80456999688425</v>
       </c>
       <c r="F81">
-        <v>1.526394912595153</v>
+        <v>0.8103222829292069</v>
       </c>
       <c r="G81">
-        <v>0.1695583707620577</v>
+        <v>-1.570252489764365</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.749389913092718</v>
       </c>
       <c r="E82">
-        <v>-8.591255410521521</v>
+        <v>-11.04397655950395</v>
       </c>
       <c r="F82">
-        <v>2.002509173071461</v>
+        <v>0.8066211622048249</v>
       </c>
       <c r="G82">
-        <v>1.388852156148872</v>
+        <v>-1.539954376988955</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.838903766286733</v>
       </c>
       <c r="E83">
-        <v>-9.565420739051568</v>
+        <v>-12.02000309085116</v>
       </c>
       <c r="F83">
-        <v>1.409018548672358</v>
+        <v>0.9145459692242769</v>
       </c>
       <c r="G83">
-        <v>1.902804419484106</v>
+        <v>-2.101158056806207</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.976716511269058</v>
       </c>
       <c r="E84">
-        <v>-11.03976960715083</v>
+        <v>-12.33988090933097</v>
       </c>
       <c r="F84">
-        <v>2.330543763042348</v>
+        <v>0.2024919933187584</v>
       </c>
       <c r="G84">
-        <v>1.809357650547098</v>
+        <v>-0.2566213986904792</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.161892609605714</v>
       </c>
       <c r="E85">
-        <v>-12.34587660891712</v>
+        <v>-14.74217297176398</v>
       </c>
       <c r="F85">
-        <v>1.892349757005323</v>
+        <v>0.3202254829254846</v>
       </c>
       <c r="G85">
-        <v>1.638576537812715</v>
+        <v>-2.336398801735739</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.401328090228492</v>
       </c>
       <c r="E86">
-        <v>-12.93275778336318</v>
+        <v>-17.6509567380589</v>
       </c>
       <c r="F86">
-        <v>1.396725823356717</v>
+        <v>-0.2067566197017801</v>
       </c>
       <c r="G86">
-        <v>2.265984507324312</v>
+        <v>-1.325311846404768</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.695659020136031</v>
       </c>
       <c r="E87">
-        <v>-12.69912928083346</v>
+        <v>-17.87823632002987</v>
       </c>
       <c r="F87">
-        <v>1.172395464140635</v>
+        <v>0.4658583277915499</v>
       </c>
       <c r="G87">
-        <v>1.453146261067057</v>
+        <v>1.267024080303692</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.042751004123798</v>
       </c>
       <c r="E88">
-        <v>-14.72974231061293</v>
+        <v>-19.05382817242109</v>
       </c>
       <c r="F88">
-        <v>1.743663527134291</v>
+        <v>-0.1692908888602291</v>
       </c>
       <c r="G88">
-        <v>2.040152332817389</v>
+        <v>0.2263938165802655</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.432008004051192</v>
       </c>
       <c r="E89">
-        <v>-17.06781155466916</v>
+        <v>-21.32435522665292</v>
       </c>
       <c r="F89">
-        <v>1.01200406384859</v>
+        <v>0.2938654898159527</v>
       </c>
       <c r="G89">
-        <v>1.766198068351619</v>
+        <v>1.094885643898208</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.857479592905833</v>
       </c>
       <c r="E90">
-        <v>-19.07994388202333</v>
+        <v>-19.96156984420663</v>
       </c>
       <c r="F90">
-        <v>1.053725212484926</v>
+        <v>-0.3713456325226979</v>
       </c>
       <c r="G90">
-        <v>2.37405726645382</v>
+        <v>0.7877928185843341</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.317016719135545</v>
       </c>
       <c r="E91">
-        <v>-18.42995389380637</v>
+        <v>-25.09528798842415</v>
       </c>
       <c r="F91">
-        <v>1.069217023749755</v>
+        <v>-0.3914721591490601</v>
       </c>
       <c r="G91">
-        <v>2.342454798735937</v>
+        <v>-1.010250537977869</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.801727458787575</v>
       </c>
       <c r="E92">
-        <v>-20.45055899602888</v>
+        <v>-25.55958789995659</v>
       </c>
       <c r="F92">
-        <v>0.9222079384431729</v>
+        <v>-1.023008942607722</v>
       </c>
       <c r="G92">
-        <v>2.118152096268157</v>
+        <v>0.7555447944862935</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.300208838904069</v>
       </c>
       <c r="E93">
-        <v>-21.71242280674024</v>
+        <v>-26.88626775913973</v>
       </c>
       <c r="F93">
-        <v>0.3782904766091565</v>
+        <v>-0.5813418694981377</v>
       </c>
       <c r="G93">
-        <v>1.672976416511282</v>
+        <v>1.017819454289514</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.790253396406726</v>
       </c>
       <c r="E94">
-        <v>-24.47685240709264</v>
+        <v>-27.58684533049637</v>
       </c>
       <c r="F94">
-        <v>0.4572049586695888</v>
+        <v>-0.4903848876567039</v>
       </c>
       <c r="G94">
-        <v>1.501821212130962</v>
+        <v>0.2478792571301355</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.26217838301666</v>
       </c>
       <c r="E95">
-        <v>-25.52087850413902</v>
+        <v>-28.25713646768971</v>
       </c>
       <c r="F95">
-        <v>0.1315237556890436</v>
+        <v>-0.8464969998024181</v>
       </c>
       <c r="G95">
-        <v>2.003587357336138</v>
+        <v>-1.244431908334834</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.70561804447955</v>
       </c>
       <c r="E96">
-        <v>-29.19116593108978</v>
+        <v>-33.01137075430147</v>
       </c>
       <c r="F96">
-        <v>0.1698027195181727</v>
+        <v>-0.4537719824506171</v>
       </c>
       <c r="G96">
-        <v>1.606497351537177</v>
+        <v>-0.3846004681476248</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.10787437341075</v>
       </c>
       <c r="E97">
-        <v>-30.39897787604558</v>
+        <v>-32.66075139002058</v>
       </c>
       <c r="F97">
-        <v>-0.1617722450266803</v>
+        <v>-0.949022953356137</v>
       </c>
       <c r="G97">
-        <v>1.830382925267009</v>
+        <v>-2.638423181828988</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.45695652307759</v>
       </c>
       <c r="E98">
-        <v>-33.74053205359452</v>
+        <v>-37.03728603778558</v>
       </c>
       <c r="F98">
-        <v>-0.3762313652718285</v>
+        <v>-1.3277527615332</v>
       </c>
       <c r="G98">
-        <v>1.66708033490584</v>
+        <v>-1.129453351210406</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.73603823299271</v>
       </c>
       <c r="E99">
-        <v>-36.12742956863846</v>
+        <v>-36.79782486073398</v>
       </c>
       <c r="F99">
-        <v>-1.102273423675466</v>
+        <v>-1.867205756391592</v>
       </c>
       <c r="G99">
-        <v>0.6773099823022368</v>
+        <v>-1.700168228361984</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.94633210603272</v>
       </c>
       <c r="E100">
-        <v>-37.90543299708506</v>
+        <v>-40.00798762918738</v>
       </c>
       <c r="F100">
-        <v>-0.5266414590318169</v>
+        <v>-1.988638783016785</v>
       </c>
       <c r="G100">
-        <v>1.697977656423858</v>
+        <v>-1.918598023043097</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.08797564371677</v>
       </c>
       <c r="E101">
-        <v>-39.29650096394626</v>
+        <v>-40.97514514419056</v>
       </c>
       <c r="F101">
-        <v>-0.9941498615636264</v>
+        <v>-2.088280016245531</v>
       </c>
       <c r="G101">
-        <v>0.6547982726351927</v>
+        <v>-1.713493174157551</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.16559704405273</v>
       </c>
       <c r="E102">
-        <v>-41.89938631102304</v>
+        <v>-42.08284611425879</v>
       </c>
       <c r="F102">
-        <v>-0.7721214188956352</v>
+        <v>-2.39003696581449</v>
       </c>
       <c r="G102">
-        <v>0.1949005968651787</v>
+        <v>-3.145125350433218</v>
       </c>
     </row>
   </sheetData>
